--- a/data/trans_dic/P2A_lim_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,51</t>
+          <t>1,05; 3,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,96</t>
+          <t>2,57; 6,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,66</t>
+          <t>2,31; 6,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 11,08</t>
+          <t>3,03; 10,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,93</t>
+          <t>2,57; 6,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 8,38</t>
+          <t>3,76; 8,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,51</t>
+          <t>1,41; 4,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 14,03</t>
+          <t>5,52; 13,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,07</t>
+          <t>2,09; 4,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,71</t>
+          <t>3,67; 6,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,69</t>
+          <t>2,11; 4,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 10,52</t>
+          <t>5,05; 10,52</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,9</t>
+          <t>2,28; 4,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,31</t>
+          <t>4,43; 8,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,66</t>
+          <t>2,55; 5,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,98; 16,36</t>
+          <t>7,75; 16,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,85</t>
+          <t>1,93; 4,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,72</t>
+          <t>4,37; 8,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,25</t>
+          <t>2,29; 5,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,97</t>
+          <t>3,61; 9,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,41</t>
+          <t>2,43; 4,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 7,62</t>
+          <t>4,92; 7,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,13</t>
+          <t>2,8; 4,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 11,1</t>
+          <t>6,06; 11,08</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 7,38</t>
+          <t>3,46; 7,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 9,83</t>
+          <t>5,26; 9,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,48</t>
+          <t>3,08; 6,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 8,16</t>
+          <t>3,88; 8,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 8,48</t>
+          <t>4,54; 8,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 11,98</t>
+          <t>7,65; 12,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,29</t>
+          <t>4,03; 7,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,97</t>
+          <t>5,4; 9,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,24</t>
+          <t>4,5; 7,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 10,28</t>
+          <t>7,04; 10,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,24</t>
+          <t>3,94; 6,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,27</t>
+          <t>5,52; 8,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 9,7</t>
+          <t>4,92; 9,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 12,47</t>
+          <t>7,08; 12,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 12,53</t>
+          <t>7,82; 12,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 15,53</t>
+          <t>4,02; 15,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,22; 13,78</t>
+          <t>8,33; 13,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,0; 15,53</t>
+          <t>9,88; 15,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 10,5</t>
+          <t>6,15; 10,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 14,11</t>
+          <t>9,93; 14,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,14; 10,81</t>
+          <t>7,28; 11,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 13,23</t>
+          <t>9,22; 12,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 10,77</t>
+          <t>7,38; 10,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 13,84</t>
+          <t>6,94; 13,83</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,33; 16,24</t>
+          <t>9,53; 15,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,05; 16,53</t>
+          <t>10,2; 17,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 13,93</t>
+          <t>7,93; 13,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,82; 22,13</t>
+          <t>16,25; 22,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 13,31</t>
+          <t>7,43; 13,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,65; 18,48</t>
+          <t>10,85; 18,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,48; 18,35</t>
+          <t>11,96; 18,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,64; 14,92</t>
+          <t>10,48; 14,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,07; 13,69</t>
+          <t>8,99; 13,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,42; 16,25</t>
+          <t>11,62; 16,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,35; 15,29</t>
+          <t>10,76; 15,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,81; 17,65</t>
+          <t>13,78; 17,55</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,43; 15,94</t>
+          <t>8,51; 15,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,25; 20,95</t>
+          <t>11,11; 20,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,89; 13,21</t>
+          <t>6,63; 13,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,66; 20,29</t>
+          <t>13,76; 19,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,11; 14,64</t>
+          <t>8,32; 14,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,3; 17,56</t>
+          <t>10,4; 17,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,98; 16,07</t>
+          <t>9,26; 16,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,94; 77,04</t>
+          <t>17,0; 78,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,93; 14,13</t>
+          <t>9,13; 13,99</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,7; 17,74</t>
+          <t>11,98; 18,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,47; 13,47</t>
+          <t>8,8; 13,21</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,67; 64,81</t>
+          <t>16,61; 67,06</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,69; 20,46</t>
+          <t>10,9; 20,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,46; 27,15</t>
+          <t>15,53; 27,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,93; 12,55</t>
+          <t>5,98; 12,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,94; 33,24</t>
+          <t>24,46; 32,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,18; 21,57</t>
+          <t>13,28; 22,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,0; 26,85</t>
+          <t>18,48; 27,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,22; 21,8</t>
+          <t>13,45; 22,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,86; 39,4</t>
+          <t>32,63; 39,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,36; 19,84</t>
+          <t>13,31; 19,88</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,47; 25,79</t>
+          <t>18,23; 25,39</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,2; 16,92</t>
+          <t>11,09; 16,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,38; 35,62</t>
+          <t>30,44; 35,61</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,81; 7,58</t>
+          <t>5,81; 7,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,53; 10,68</t>
+          <t>8,47; 10,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,06</t>
+          <t>6,12; 7,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,22; 14,51</t>
+          <t>9,85; 14,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,16; 9,11</t>
+          <t>7,1; 8,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,46; 12,66</t>
+          <t>10,45; 12,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,77; 9,71</t>
+          <t>7,79; 9,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,52; 33,16</t>
+          <t>13,43; 33,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,76; 8,02</t>
+          <t>6,77; 8,05</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,8; 11,25</t>
+          <t>9,81; 11,36</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,56</t>
+          <t>7,23; 8,62</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,02; 27,71</t>
+          <t>13,0; 26,03</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5179; 17327</t>
+          <t>5156; 19677</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12571; 31518</t>
+          <t>11642; 30145</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9504; 27685</t>
+          <t>9580; 28141</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11471; 43670</t>
+          <t>11943; 42196</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11468; 27741</t>
+          <t>12033; 28953</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16520; 36052</t>
+          <t>16167; 35102</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5405; 17840</t>
+          <t>5573; 17871</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17247; 43929</t>
+          <t>17282; 43195</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19333; 39114</t>
+          <t>20062; 41416</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32763; 59299</t>
+          <t>32449; 57632</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16999; 38032</t>
+          <t>17141; 37510</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34130; 74389</t>
+          <t>35709; 74419</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16322; 35867</t>
+          <t>16665; 35889</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31341; 57096</t>
+          <t>30409; 57500</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14064; 33042</t>
+          <t>14846; 32429</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33472; 68621</t>
+          <t>32500; 67809</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12367; 30338</t>
+          <t>12086; 29409</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25852; 53117</t>
+          <t>26618; 50551</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12751; 29437</t>
+          <t>12823; 30257</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17635; 45814</t>
+          <t>18430; 46005</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32689; 59825</t>
+          <t>32993; 59783</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63719; 98811</t>
+          <t>63810; 100038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32101; 58661</t>
+          <t>32042; 56517</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56160; 103217</t>
+          <t>56330; 103064</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21915; 47075</t>
+          <t>22054; 46245</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38243; 67013</t>
+          <t>35882; 65260</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20868; 43312</t>
+          <t>20586; 42419</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21378; 43509</t>
+          <t>20691; 44360</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30724; 58344</t>
+          <t>31191; 56803</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53045; 85062</t>
+          <t>54278; 87190</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25353; 48067</t>
+          <t>26573; 48168</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32534; 58783</t>
+          <t>31837; 58355</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>59433; 95955</t>
+          <t>59645; 93659</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>98190; 143125</t>
+          <t>98037; 139963</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51826; 82856</t>
+          <t>52359; 85835</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58947; 92783</t>
+          <t>61936; 94674</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25606; 50081</t>
+          <t>25421; 49071</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44736; 76501</t>
+          <t>43446; 75584</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47723; 80527</t>
+          <t>50242; 80658</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39935; 137309</t>
+          <t>35545; 136427</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42185; 70743</t>
+          <t>42766; 71301</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61609; 95716</t>
+          <t>60868; 95701</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39942; 68049</t>
+          <t>39844; 68942</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>67972; 99607</t>
+          <t>70113; 99336</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73551; 111317</t>
+          <t>74946; 114208</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>113689; 162649</t>
+          <t>113362; 159738</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94919; 138990</t>
+          <t>95277; 139432</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>107907; 220089</t>
+          <t>110395; 219972</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36016; 62684</t>
+          <t>36767; 61431</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43055; 70786</t>
+          <t>43665; 73970</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37888; 66411</t>
+          <t>37829; 66715</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88262; 123514</t>
+          <t>90710; 127075</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>29185; 53780</t>
+          <t>30009; 54446</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52153; 82755</t>
+          <t>48587; 81162</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>56885; 90949</t>
+          <t>59295; 92684</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>57875; 81192</t>
+          <t>57039; 80161</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71647; 108166</t>
+          <t>71009; 106488</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100054; 142367</t>
+          <t>101830; 145265</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100646; 148723</t>
+          <t>104594; 149896</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>152211; 194521</t>
+          <t>151833; 193389</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24591; 46516</t>
+          <t>24837; 46283</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34854; 64896</t>
+          <t>34420; 62563</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23034; 44158</t>
+          <t>22170; 43654</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50111; 74415</t>
+          <t>50478; 72312</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27803; 50221</t>
+          <t>28526; 49225</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36451; 62159</t>
+          <t>36799; 62774</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33935; 60716</t>
+          <t>34991; 60457</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>102918; 468152</t>
+          <t>103296; 478204</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56681; 89650</t>
+          <t>57970; 88774</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>77645; 117724</t>
+          <t>79533; 119534</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>60312; 95904</t>
+          <t>62699; 94060</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>162407; 631511</t>
+          <t>161872; 653461</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22436; 42933</t>
+          <t>22880; 43660</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>38616; 67828</t>
+          <t>38795; 67975</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15245; 32266</t>
+          <t>15371; 32683</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>70153; 93488</t>
+          <t>68795; 92518</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>44015; 72009</t>
+          <t>44338; 73748</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>70003; 104430</t>
+          <t>71873; 105834</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52920; 87229</t>
+          <t>53824; 89526</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>139525; 167274</t>
+          <t>138536; 166182</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>72666; 107863</t>
+          <t>72405; 108085</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>118014; 164768</t>
+          <t>116461; 162176</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73580; 111160</t>
+          <t>72908; 110767</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>214440; 251453</t>
+          <t>214842; 251348</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>189845; 247810</t>
+          <t>189776; 248188</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>291937; 365686</t>
+          <t>290109; 363057</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>207562; 272160</t>
+          <t>206871; 269362</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>351263; 498687</t>
+          <t>338505; 500210</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>241531; 307359</t>
+          <t>239778; 302984</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>372104; 450408</t>
+          <t>371795; 454340</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>274838; 343545</t>
+          <t>275698; 343640</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>499800; 1225374</t>
+          <t>496321; 1231422</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>448730; 532442</t>
+          <t>449897; 534914</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>683949; 785386</t>
+          <t>684420; 792609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>501359; 591663</t>
+          <t>500086; 596343</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>928987; 1976213</t>
+          <t>927262; 1857005</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_lim_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,99</t>
+          <t>0,92; 3,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,65</t>
+          <t>2,39; 6,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,77</t>
+          <t>2,25; 6,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 10,71</t>
+          <t>3,15; 10,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,19</t>
+          <t>2,42; 6,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 8,16</t>
+          <t>3,7; 8,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,52</t>
+          <t>1,39; 4,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,52; 13,79</t>
+          <t>5,99; 15,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,31</t>
+          <t>2,06; 4,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 6,52</t>
+          <t>3,77; 6,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,62</t>
+          <t>2,29; 4,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 10,52</t>
+          <t>5,52; 11,01</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,9</t>
+          <t>2,31; 4,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 8,37</t>
+          <t>4,51; 8,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,56</t>
+          <t>2,34; 5,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 16,16</t>
+          <t>7,36; 15,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,7</t>
+          <t>2,07; 4,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,3</t>
+          <t>4,16; 8,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,4</t>
+          <t>2,37; 5,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,01</t>
+          <t>4,76; 9,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,4</t>
+          <t>2,46; 4,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 7,72</t>
+          <t>4,96; 7,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,94</t>
+          <t>2,66; 4,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 11,08</t>
+          <t>6,71; 11,49</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 7,25</t>
+          <t>3,39; 7,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,26; 9,57</t>
+          <t>5,48; 9,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,35</t>
+          <t>3,2; 6,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,32</t>
+          <t>4,03; 8,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 8,26</t>
+          <t>4,49; 8,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,65; 12,28</t>
+          <t>7,49; 12,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,3</t>
+          <t>3,87; 7,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,9</t>
+          <t>7,0; 10,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,07</t>
+          <t>4,5; 7,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 10,06</t>
+          <t>7,06; 10,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 6,47</t>
+          <t>3,94; 6,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,52; 8,43</t>
+          <t>5,79; 8,52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 9,5</t>
+          <t>4,93; 9,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 12,32</t>
+          <t>7,34; 12,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,55</t>
+          <t>7,55; 12,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 15,43</t>
+          <t>11,67; 17,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,33; 13,89</t>
+          <t>8,33; 13,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,88; 15,53</t>
+          <t>10,1; 15,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 10,64</t>
+          <t>6,31; 10,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 14,07</t>
+          <t>10,86; 14,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 11,09</t>
+          <t>7,09; 10,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,22; 12,99</t>
+          <t>9,39; 13,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 10,8</t>
+          <t>7,41; 10,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 13,83</t>
+          <t>11,8; 15,09</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,53; 15,92</t>
+          <t>9,19; 15,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,2; 17,27</t>
+          <t>10,12; 16,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 13,99</t>
+          <t>7,96; 14,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,25; 22,77</t>
+          <t>15,56; 21,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 13,48</t>
+          <t>7,24; 13,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,85; 18,12</t>
+          <t>11,33; 18,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,96; 18,7</t>
+          <t>11,82; 18,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,48; 14,74</t>
+          <t>11,16; 15,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,99; 13,48</t>
+          <t>9,2; 13,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,62; 16,58</t>
+          <t>11,64; 16,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,76; 15,41</t>
+          <t>10,69; 15,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,78; 17,55</t>
+          <t>13,93; 17,7</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,51; 15,86</t>
+          <t>8,4; 16,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,11; 20,2</t>
+          <t>11,61; 20,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,63; 13,06</t>
+          <t>6,91; 13,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,76; 19,72</t>
+          <t>13,49; 19,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,32; 14,35</t>
+          <t>8,29; 14,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,4; 17,73</t>
+          <t>10,33; 18,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,26; 16,0</t>
+          <t>8,86; 15,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,0; 78,7</t>
+          <t>15,5; 20,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,13; 13,99</t>
+          <t>9,1; 14,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,98; 18,01</t>
+          <t>11,98; 17,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,8; 13,21</t>
+          <t>8,97; 13,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,61; 67,06</t>
+          <t>15,42; 19,52</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,9; 20,8</t>
+          <t>10,91; 20,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,53; 27,21</t>
+          <t>15,15; 26,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,98; 12,72</t>
+          <t>6,02; 12,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,46; 32,89</t>
+          <t>24,09; 32,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,28; 22,09</t>
+          <t>12,95; 21,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,48; 27,21</t>
+          <t>18,43; 27,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,45; 22,37</t>
+          <t>13,09; 21,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,63; 39,14</t>
+          <t>32,61; 39,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,31; 19,88</t>
+          <t>13,57; 19,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,23; 25,39</t>
+          <t>18,47; 25,42</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,09; 16,86</t>
+          <t>11,33; 17,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,44; 35,61</t>
+          <t>30,43; 35,61</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,81; 7,6</t>
+          <t>5,79; 7,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,47; 10,6</t>
+          <t>8,52; 10,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,12; 7,97</t>
+          <t>6,06; 7,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,85; 14,55</t>
+          <t>12,22; 14,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,98</t>
+          <t>7,24; 9,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,45; 12,78</t>
+          <t>10,45; 12,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,79; 9,71</t>
+          <t>7,8; 9,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,43; 33,32</t>
+          <t>13,53; 15,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,77; 8,05</t>
+          <t>6,75; 8,01</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,81; 11,36</t>
+          <t>9,8; 11,37</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,23; 8,62</t>
+          <t>7,26; 8,58</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,0; 26,03</t>
+          <t>13,26; 14,85</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23356</t>
+          <t>25186</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28788</t>
+          <t>35375</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52144</t>
+          <t>60561</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5156; 19677</t>
+          <t>4542; 17446</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11642; 30145</t>
+          <t>10820; 29063</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9580; 28141</t>
+          <t>9363; 26174</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11943; 42196</t>
+          <t>12673; 41543</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12033; 28953</t>
+          <t>11310; 28265</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16167; 35102</t>
+          <t>15911; 35060</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5573; 17871</t>
+          <t>5510; 18237</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17282; 43195</t>
+          <t>21702; 54649</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20062; 41416</t>
+          <t>19833; 40429</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32449; 57632</t>
+          <t>33328; 58455</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17141; 37510</t>
+          <t>18556; 38608</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35709; 74419</t>
+          <t>42240; 84210</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48270</t>
+          <t>50490</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30917</t>
+          <t>34424</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79187</t>
+          <t>84913</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16665; 35889</t>
+          <t>16906; 34967</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30409; 57500</t>
+          <t>30971; 55827</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14846; 32429</t>
+          <t>13641; 31940</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32500; 67809</t>
+          <t>34505; 74836</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12086; 29409</t>
+          <t>12919; 30907</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26618; 50551</t>
+          <t>25333; 50392</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12823; 30257</t>
+          <t>13268; 31751</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18430; 46005</t>
+          <t>23802; 47303</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32993; 59783</t>
+          <t>33400; 60722</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63810; 100038</t>
+          <t>64359; 99170</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32042; 56517</t>
+          <t>30452; 54367</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56330; 103064</t>
+          <t>64993; 111352</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31230</t>
+          <t>35633</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45734</t>
+          <t>53819</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76964</t>
+          <t>89452</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22054; 46245</t>
+          <t>21616; 46187</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35882; 65260</t>
+          <t>37333; 65392</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20586; 42419</t>
+          <t>21353; 43891</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20691; 44360</t>
+          <t>24868; 49753</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31191; 56803</t>
+          <t>30854; 56854</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54278; 87190</t>
+          <t>53183; 85509</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26573; 48168</t>
+          <t>25493; 48732</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31837; 58355</t>
+          <t>43424; 66023</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>59645; 93659</t>
+          <t>59595; 95239</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>98037; 139963</t>
+          <t>98268; 140996</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52359; 85835</t>
+          <t>52331; 84011</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61936; 94674</t>
+          <t>71626; 105523</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92294</t>
+          <t>98222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>84373</t>
+          <t>91422</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>176667</t>
+          <t>189643</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25421; 49071</t>
+          <t>25466; 49345</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43446; 75584</t>
+          <t>45040; 75017</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50242; 80658</t>
+          <t>48523; 80263</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35545; 136427</t>
+          <t>81348; 119936</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42766; 71301</t>
+          <t>42760; 71078</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60868; 95701</t>
+          <t>62233; 96500</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39844; 68942</t>
+          <t>40921; 69753</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70113; 99336</t>
+          <t>79185; 107071</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74946; 114208</t>
+          <t>73032; 112159</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>113362; 159738</t>
+          <t>115476; 162075</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>95277; 139432</t>
+          <t>95635; 137340</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>110395; 219972</t>
+          <t>168281; 215189</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104847</t>
+          <t>110711</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68423</t>
+          <t>79172</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>173270</t>
+          <t>189883</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36767; 61431</t>
+          <t>35472; 60764</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43665; 73970</t>
+          <t>43327; 72140</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37829; 66715</t>
+          <t>37950; 67355</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90710; 127075</t>
+          <t>94322; 131010</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30009; 54446</t>
+          <t>29257; 54939</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>48587; 81162</t>
+          <t>50746; 81236</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59295; 92684</t>
+          <t>58576; 90971</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>57039; 80161</t>
+          <t>67491; 92742</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71009; 106488</t>
+          <t>72628; 108729</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>101830; 145265</t>
+          <t>102005; 141956</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>104594; 149896</t>
+          <t>103932; 146671</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>151833; 193389</t>
+          <t>168637; 214287</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61269</t>
+          <t>67175</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>276398</t>
+          <t>78741</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>337667</t>
+          <t>145916</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24837; 46283</t>
+          <t>24511; 47201</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34420; 62563</t>
+          <t>35954; 64100</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22170; 43654</t>
+          <t>23117; 43831</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50478; 72312</t>
+          <t>54728; 80014</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28526; 49225</t>
+          <t>28430; 50626</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36799; 62774</t>
+          <t>36584; 64867</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34991; 60457</t>
+          <t>33464; 60131</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>103296; 478204</t>
+          <t>67942; 89989</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>57970; 88774</t>
+          <t>57760; 89164</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>79533; 119534</t>
+          <t>79530; 117554</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>62699; 94060</t>
+          <t>63907; 98170</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>161872; 653461</t>
+          <t>130131; 164738</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80941</t>
+          <t>87294</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>151994</t>
+          <t>166305</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>232935</t>
+          <t>253599</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22880; 43660</t>
+          <t>22908; 42398</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>38795; 67975</t>
+          <t>37858; 66972</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15371; 32683</t>
+          <t>15476; 33222</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68795; 92518</t>
+          <t>74300; 101188</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>44338; 73748</t>
+          <t>43230; 73198</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>71873; 105834</t>
+          <t>71675; 105557</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53824; 89526</t>
+          <t>52367; 87918</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>138536; 166182</t>
+          <t>151061; 182745</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>72405; 108085</t>
+          <t>73819; 108603</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>116461; 162176</t>
+          <t>117981; 162382</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72908; 110767</t>
+          <t>74465; 112094</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>214842; 251348</t>
+          <t>234870; 274795</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>442206</t>
+          <t>474711</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>686628</t>
+          <t>539257</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1128833</t>
+          <t>1013967</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>189776; 248188</t>
+          <t>189238; 250372</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>290109; 363057</t>
+          <t>291578; 364317</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>206871; 269362</t>
+          <t>204528; 268352</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>338505; 500210</t>
+          <t>428364; 515490</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>239778; 302984</t>
+          <t>244338; 305926</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>371795; 454340</t>
+          <t>371725; 453782</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>275698; 343640</t>
+          <t>275777; 345368</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>496321; 1231422</t>
+          <t>503319; 576475</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>449897; 534914</t>
+          <t>448197; 532244</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>684420; 792609</t>
+          <t>683989; 793306</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>500086; 596343</t>
+          <t>501779; 593632</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>927262; 1857005</t>
+          <t>957866; 1073169</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_lim_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_lim_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica) (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación (tasa de respuesta: 99,66%)</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica) (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
